--- a/file/XLK-224-滯洪池期望.xlsx
+++ b/file/XLK-224-滯洪池期望.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9CB3AA-64D4-ED4A-999F-A2D979C2B809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD34DFB-7D6D-7149-8369-32519BD93D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="1260" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
+    <workbookView xWindow="1960" yWindow="900" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A.乾式-兒童遊戲廠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>B.濕式-生態公園</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -66,6 +62,10 @@
   </si>
   <si>
     <t>E.乾式-滑板/越野自行車運動場</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A.乾式-兒童遊戲場</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -183,7 +183,17 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" baseline="0">
@@ -199,6 +209,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.38993865030674846"/>
+          <c:y val="1.6686531585220502E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -496,8 +514,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.21069090865175599"/>
-                  <c:y val="5.802164181205597E-2"/>
+                  <c:x val="-0.13016943625911792"/>
+                  <c:y val="9.8546169511886106E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -523,12 +541,12 @@
               </c:spPr>
               <c:txPr>
                 <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
+                  <a:noAutofit/>
                 </a:bodyPr>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent1"/>
                       </a:solidFill>
@@ -552,8 +570,8 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.29356589053668902"/>
-                      <c:h val="0.11127532777115613"/>
+                      <c:w val="0.3227069948311676"/>
+                      <c:h val="0.1875566150178784"/>
                     </c:manualLayout>
                   </c15:layout>
                 </c:ext>
@@ -564,6 +582,12 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.15129450268102987"/>
+                  <c:y val="-0.12215855020506226"/>
+                </c:manualLayout>
+              </c:layout>
               <c:spPr>
                 <a:solidFill>
                   <a:schemeClr val="lt1">
@@ -592,7 +616,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent2"/>
                       </a:solidFill>
@@ -605,7 +629,7 @@
                   <a:endParaRPr lang="zh-TW"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="inEnd"/>
+              <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="1"/>
@@ -613,6 +637,14 @@
               <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.24430981595092024"/>
+                      <c:h val="0.21539928486293206"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-C162-DD49-86C7-435924432D3F}"/>
                 </c:ext>
@@ -622,8 +654,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.10222863629776337"/>
-                  <c:y val="7.3576342289752558E-2"/>
+                  <c:x val="6.1584464518622296E-2"/>
+                  <c:y val="0.14207515199840526"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -654,7 +686,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent3"/>
                       </a:solidFill>
@@ -675,7 +707,14 @@
               <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.25280674846625767"/>
+                      <c:h val="0.14598331346841478"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-C162-DD49-86C7-435924432D3F}"/>
                 </c:ext>
@@ -685,8 +724,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.17614777063909959"/>
-                  <c:y val="0.12410819029027806"/>
+                  <c:x val="4.8847157142167037E-2"/>
+                  <c:y val="0.16896018140137545"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -717,7 +756,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent4"/>
                       </a:solidFill>
@@ -741,7 +780,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.24891877203999807"/>
+                      <c:w val="0.34094331191729871"/>
                       <c:h val="0.1633373063170441"/>
                     </c:manualLayout>
                   </c15:layout>
@@ -755,8 +794,8 @@
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.29812974010917354"/>
-                  <c:y val="0.10206657719632484"/>
+                  <c:x val="-5.3864124921501381E-2"/>
+                  <c:y val="4.5951941924980887E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -787,7 +826,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent5"/>
                       </a:solidFill>
@@ -811,7 +850,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.30055214723926377"/>
+                      <c:w val="0.38490797546012262"/>
                       <c:h val="0.1633373063170441"/>
                     </c:manualLayout>
                   </c15:layout>
@@ -821,6 +860,27 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF">
+                  <a:alpha val="90000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:srgbClr val="4472C4">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
@@ -828,7 +888,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="accent1"/>
                     </a:solidFill>
@@ -873,7 +933,7 @@
                 <c:ptCount val="5"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>A.乾式-兒童遊戲廠</c:v>
+                    <c:v>A.乾式-兒童遊戲場</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>B.濕式-生態公園</c:v>
@@ -1615,14 +1675,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2209800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1969,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>118</v>
@@ -1980,7 +2040,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>70</v>
@@ -1991,7 +2051,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -2002,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>19</v>
@@ -2013,7 +2073,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>16</v>

--- a/file/XLK-224-滯洪池期望.xlsx
+++ b/file/XLK-224-滯洪池期望.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD34DFB-7D6D-7149-8369-32519BD93D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144BB365-BFA3-9749-8F7C-9BD60D331199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="900" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
+    <workbookView xWindow="1480" yWindow="700" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,6 +66,14 @@
   </si>
   <si>
     <t>A.乾式-兒童遊戲場</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F.乾式-寵物公園</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G.濕式-循環水噴泉＋蓄水池, 過濾儲存水改善水質</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -975,19 +983,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>118</c:v>
+                  <c:v>191</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70</c:v>
+                  <c:v>109</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1005,6 +1013,927 @@
           <c:showCatName val="1"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2400">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7 滯洪池票選結果</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" sz="2400">
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2400">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/04/22</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" sz="1600">
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.0018747656542937E-2"/>
+          <c:y val="0.27979907199100112"/>
+          <c:w val="0.84743117636611209"/>
+          <c:h val="0.70790185601799771"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vote</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-D205-1141-8815-837664C3F95C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.2606516290726815E-2"/>
+                  <c:y val="-0.16480162767039674"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.28119047619047621"/>
+                      <c:h val="0.16135714285714287"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.32657894736842108"/>
+                      <c:h val="0.16135714285714287"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.5062656641604009E-3"/>
+                  <c:y val="-5.3968253968253999E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.24310776942355888"/>
+                  <c:y val="-3.6507874015748044E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.4780763917668186"/>
+                      <c:h val="0.18965079365079363"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-D205-1141-8815-837664C3F95C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>工作表1!$A$2:$B$8</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="7"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>A.乾式-兒童遊戲場</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>B.濕式-生態公園</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>C-濕式-儲水池</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>D.乾濕結合-蓄水池+停車場</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>E.乾式-滑板/越野自行車運動場</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>F.乾式-寵物公園</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>G.濕式-循環水噴泉＋蓄水池, 過濾儲存水改善水質</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>7</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D205-1141-8815-837664C3F95C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
@@ -1101,6 +2030,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="263">
   <cs:axisTitle>
@@ -1669,20 +2638,540 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="259">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="10000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d>
+        <a:bevelT w="127000" h="127000"/>
+        <a:bevelB w="127000" h="127000"/>
+      </a:sp3d>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2209800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1702,6 +3191,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD77A93B-A246-2128-68C1-68B68BDEA72A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2007,10 +3532,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2927543E-66F7-6A45-9BB9-2C455A1B52E6}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="45.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2032,7 +3557,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>118</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2043,7 +3568,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2054,7 +3579,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2065,7 +3590,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2076,7 +3601,29 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/file/XLK-224-滯洪池期望.xlsx
+++ b/file/XLK-224-滯洪池期望.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144BB365-BFA3-9749-8F7C-9BD60D331199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511EEA11-48C4-444B-830C-3EFCBFF86E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="700" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
+    <workbookView xWindow="2680" yWindow="1020" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -983,19 +983,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>191</c:v>
+                  <c:v>241</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>109</c:v>
+                  <c:v>142</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1116,9 +1116,16 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2400">
+              <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1126,7 +1133,7 @@
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
               </a:rPr>
-              <a:t>2022/04/22</a:t>
+              <a:t>2022/04/24</a:t>
             </a:r>
             <a:endParaRPr lang="zh-TW" sz="1600">
               <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
@@ -1467,32 +1474,6 @@
                   <c:y val="-0.16480162767039674"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="accent1"/>
-                      </a:solidFill>
-                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
-                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="zh-TW"/>
-                </a:p>
-              </c:txPr>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
@@ -1792,6 +1773,13 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
@@ -1898,25 +1886,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>191</c:v>
+                  <c:v>241</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>109</c:v>
+                  <c:v>142</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3557,7 +3545,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>191</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3568,7 +3556,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>109</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3579,7 +3567,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3590,7 +3578,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3601,7 +3589,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3612,7 +3600,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3623,7 +3611,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/file/XLK-224-滯洪池期望.xlsx
+++ b/file/XLK-224-滯洪池期望.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511EEA11-48C4-444B-830C-3EFCBFF86E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893D8E65-3147-9742-9E19-59EC75267C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="1020" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
+    <workbookView xWindow="-1640" yWindow="780" windowWidth="27700" windowHeight="16880" xr2:uid="{7DB694E0-A37F-3D40-92A6-1BFFC028236A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -983,19 +983,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>241</c:v>
+                  <c:v>260</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>142</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1133,7 +1133,7 @@
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
               </a:rPr>
-              <a:t>2022/04/24</a:t>
+              <a:t>2022/04/27</a:t>
             </a:r>
             <a:endParaRPr lang="zh-TW" sz="1600">
               <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
@@ -1474,6 +1474,32 @@
                   <c:y val="-0.16480162767039674"/>
                 </c:manualLayout>
               </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
@@ -1886,25 +1912,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>241</c:v>
+                  <c:v>260</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>142</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3545,7 +3571,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3556,7 +3582,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3567,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3578,7 +3604,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3589,7 +3615,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3600,7 +3626,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3611,7 +3637,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
